--- a/artfynd/A 36424-2025 artfynd.xlsx
+++ b/artfynd/A 36424-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -1008,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">

--- a/artfynd/A 36424-2025 artfynd.xlsx
+++ b/artfynd/A 36424-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109573811</v>
+        <v>109573843</v>
       </c>
       <c r="B2" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,14 +710,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Olseröd, Kungälvs kommun, Boh</t>
+          <t>Olseröd, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>321766.3667199005</v>
+        <v>321717</v>
       </c>
       <c r="R2" t="n">
-        <v>6421953.041292675</v>
+        <v>6421920</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,26 +747,16 @@
           <t>2023-04-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-04-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
@@ -792,61 +777,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109573850</v>
+        <v>109573811</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Olseröd, Boh</t>
+          <t>Olseröd, Kungälvs kommun, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>321646.489453216</v>
+        <v>321766</v>
       </c>
       <c r="R3" t="n">
-        <v>6421751.373406505</v>
+        <v>6421953</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,7 +851,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,15 +861,16 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -912,43 +889,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109573843</v>
+        <v>109573850</v>
       </c>
       <c r="B4" t="n">
-        <v>94134</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -956,13 +932,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>321717.402502574</v>
+        <v>321647</v>
       </c>
       <c r="R4" t="n">
-        <v>6421919.035873599</v>
+        <v>6421751</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,19 +965,9 @@
           <t>2023-04-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-04-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +976,6 @@
       <c r="AE4" t="b">
         <v>1</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36424-2025 artfynd.xlsx
+++ b/artfynd/A 36424-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134894134</v>
+        <v>135381716</v>
       </c>
       <c r="B6" t="n">
-        <v>98060</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,37 +1125,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grinsvalls gamla tomt, Grinsvalls gamla tomt, Boh</t>
+          <t>Rätsvik, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>321780</v>
+        <v>321805</v>
       </c>
       <c r="R6" t="n">
-        <v>6421911</v>
+        <v>6421950</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1179,22 +1187,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,58 +1217,54 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134984523</v>
+        <v>135381794</v>
       </c>
       <c r="B7" t="n">
-        <v>98060</v>
+        <v>58563</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>102987</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1268,13 +1272,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>321789</v>
+        <v>321814</v>
       </c>
       <c r="R7" t="n">
-        <v>6421986</v>
+        <v>6421975</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,22 +1302,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,7 +1326,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1338,6 +1341,574 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135381962</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58563</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102987</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sädesärla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Motacilla alba</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rätsvik, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>321827</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6421967</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135368736</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58260</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rätsvik, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>321766</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6421912</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135381412</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58134</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rätsvik, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>321701</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6421894</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134894134</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Grinsvalls gamla tomt, Grinsvalls gamla tomt, Boh</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>321780</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6421911</v>
+      </c>
+      <c r="S11" t="n">
+        <v>7</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134984523</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rätsvik, Boh</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>321789</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6421986</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36424-2025 artfynd.xlsx
+++ b/artfynd/A 36424-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109573811</v>
+        <v>135488702</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
+        <v>96783</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,38 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Olseröd, Kungälvs kommun, Boh</t>
+          <t>Rätsvik, Rätsvik, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>321766</v>
+        <v>321409</v>
       </c>
       <c r="R3" t="n">
-        <v>6421953</v>
+        <v>6421493</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -846,22 +842,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera kuddar varav största 30x20cm</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,29 +871,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ville Henrik-Klemens</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ville Henrik-Klemens</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134984551</v>
+        <v>109573811</v>
       </c>
       <c r="B4" t="n">
-        <v>96423</v>
+        <v>96348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,32 +917,24 @@
           <t>(Hedw.) Warnst.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rätsvik, Boh</t>
+          <t>Olseröd, Kungälvs kommun, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>321761</v>
+        <v>321766</v>
       </c>
       <c r="R4" t="n">
-        <v>6422058</v>
+        <v>6421953</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,7 +958,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -976,12 +968,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,22 +989,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Ville Henrik-Klemens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Ville Henrik-Klemens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109573850</v>
+        <v>134984551</v>
       </c>
       <c r="B5" t="n">
-        <v>57950</v>
+        <v>96423</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,45 +1012,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Olseröd, Boh</t>
+          <t>Rätsvik, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>321647</v>
+        <v>321761</v>
       </c>
       <c r="R5" t="n">
-        <v>6421751</v>
+        <v>6422058</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,42 +1078,53 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ville Henrik-Klemens</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ville Henrik-Klemens</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135381716</v>
+        <v>109573850</v>
       </c>
       <c r="B6" t="n">
-        <v>57972</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,23 +1154,23 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rätsvik, Boh</t>
+          <t>Olseröd, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>321805</v>
+        <v>321647</v>
       </c>
       <c r="R6" t="n">
-        <v>6421950</v>
+        <v>6421751</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1187,29 +1194,19 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1217,44 +1214,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Ville Henrik-Klemens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Ville Henrik-Klemens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135381794</v>
+        <v>135381716</v>
       </c>
       <c r="B7" t="n">
-        <v>58563</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102987</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>321814</v>
+        <v>321805</v>
       </c>
       <c r="R7" t="n">
-        <v>6421975</v>
+        <v>6421950</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1317,7 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135381962</v>
+        <v>135381794</v>
       </c>
       <c r="B8" t="n">
         <v>58563</v>
@@ -1387,10 +1384,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>321827</v>
+        <v>321814</v>
       </c>
       <c r="R8" t="n">
-        <v>6421967</v>
+        <v>6421975</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,22 +1414,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1456,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135368736</v>
+        <v>135381962</v>
       </c>
       <c r="B9" t="n">
-        <v>58260</v>
+        <v>58563</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,21 +1467,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103012</v>
+        <v>102987</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1502,13 +1499,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>321766</v>
+        <v>321827</v>
       </c>
       <c r="R9" t="n">
-        <v>6421912</v>
+        <v>6421967</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1532,22 +1529,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135381412</v>
+        <v>135368736</v>
       </c>
       <c r="B10" t="n">
-        <v>58134</v>
+        <v>58260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,27 +1582,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103020</v>
+        <v>103012</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1613,13 +1614,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>321701</v>
+        <v>321766</v>
       </c>
       <c r="R10" t="n">
-        <v>6421894</v>
+        <v>6421912</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1643,7 +1644,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1653,7 +1654,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1685,48 +1686,52 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134894134</v>
+        <v>135381412</v>
       </c>
       <c r="B11" t="n">
-        <v>98060</v>
+        <v>58134</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>103020</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grinsvalls gamla tomt, Grinsvalls gamla tomt, Boh</t>
+          <t>Rätsvik, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>321780</v>
+        <v>321701</v>
       </c>
       <c r="R11" t="n">
-        <v>6421911</v>
+        <v>6421894</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1750,22 +1755,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,22 +1785,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134984523</v>
+        <v>135489134</v>
       </c>
       <c r="B12" t="n">
-        <v>98060</v>
+        <v>30293</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,49 +1808,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>200985</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Latreille, 1798)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rätsvik, Boh</t>
+          <t>Rätsvik, Rätsvik, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>321789</v>
+        <v>321409</v>
       </c>
       <c r="R12" t="n">
-        <v>6421986</v>
+        <v>6421493</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1869,22 +1862,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1893,22 +1886,686 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135485432</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56539</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fröjdens, Fröjdens, Boh</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>321811</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6421891</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135484109</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56706</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fröjdens, Fröjdens, Boh</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>321811</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6421891</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135486564</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56706</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Marielund, Boh</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>321632</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6421605</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134894134</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Grinsvalls gamla tomt, Grinsvalls gamla tomt, Boh</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>321780</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6421911</v>
+      </c>
+      <c r="S16" t="n">
+        <v>7</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134984523</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Rätsvik, Boh</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>321789</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6421986</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Inka Eriksson</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Inka Eriksson</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135484279</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fröjdens, Fröjdens, Boh</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>321819</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6421968</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36424-2025 artfynd.xlsx
+++ b/artfynd/A 36424-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1686,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135381412</v>
+        <v>135531138</v>
       </c>
       <c r="B11" t="n">
-        <v>58134</v>
+        <v>58260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,27 +1697,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103020</v>
+        <v>103012</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1725,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>321701</v>
+        <v>321805</v>
       </c>
       <c r="R11" t="n">
-        <v>6421894</v>
+        <v>6421950</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1755,22 +1759,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,45 +1801,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135489134</v>
+        <v>135381412</v>
       </c>
       <c r="B12" t="n">
-        <v>30293</v>
+        <v>58134</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>200985</v>
+        <v>103020</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rätsvik, Rätsvik, Boh</t>
+          <t>Rätsvik, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>321409</v>
+        <v>321701</v>
       </c>
       <c r="R12" t="n">
-        <v>6421493</v>
+        <v>6421894</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1862,22 +1870,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,62 +1900,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135485432</v>
+        <v>135489134</v>
       </c>
       <c r="B13" t="n">
-        <v>56539</v>
+        <v>30293</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>206004</v>
+        <v>200985</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fröjdens, Fröjdens, Boh</t>
+          <t>Rätsvik, Rätsvik, Boh</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>321811</v>
+        <v>321409</v>
       </c>
       <c r="R13" t="n">
-        <v>6421891</v>
+        <v>6421493</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1989,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2016,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135484109</v>
+        <v>135485432</v>
       </c>
       <c r="B14" t="n">
-        <v>56706</v>
+        <v>56539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,21 +2030,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>206046</v>
+        <v>206004</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2091,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2101,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2128,7 +2131,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135486564</v>
+        <v>135484109</v>
       </c>
       <c r="B15" t="n">
         <v>56706</v>
@@ -2157,19 +2160,24 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Marielund, Boh</t>
+          <t>Fröjdens, Fröjdens, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>321632</v>
+        <v>321811</v>
       </c>
       <c r="R15" t="n">
-        <v>6421605</v>
+        <v>6421891</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2198,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2208,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2223,60 +2231,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134894134</v>
+        <v>135486564</v>
       </c>
       <c r="B16" t="n">
-        <v>98060</v>
+        <v>56706</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>206046</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Grinsvalls gamla tomt, Grinsvalls gamla tomt, Boh</t>
+          <t>Marielund, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>321780</v>
+        <v>321632</v>
       </c>
       <c r="R16" t="n">
-        <v>6421911</v>
+        <v>6421605</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2300,22 +2308,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2342,7 +2350,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134984523</v>
+        <v>134894134</v>
       </c>
       <c r="B17" t="n">
         <v>98060</v>
@@ -2370,32 +2378,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rätsvik, Boh</t>
+          <t>Grinsvalls gamla tomt, Grinsvalls gamla tomt, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>321789</v>
+        <v>321780</v>
       </c>
       <c r="R17" t="n">
-        <v>6421986</v>
+        <v>6421911</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2424,7 +2420,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2434,7 +2430,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2443,26 +2439,25 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135484279</v>
+        <v>134984523</v>
       </c>
       <c r="B18" t="n">
         <v>98060</v>
@@ -2490,20 +2485,32 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fröjdens, Fröjdens, Boh</t>
+          <t>Rätsvik, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>321819</v>
+        <v>321789</v>
       </c>
       <c r="R18" t="n">
-        <v>6421968</v>
+        <v>6421986</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2527,22 +2534,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2551,21 +2558,129 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135484279</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fröjdens, Fröjdens, Boh</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>321819</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6421968</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
           <t>Mats Eriksson</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>Mats Eriksson</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36424-2025 artfynd.xlsx
+++ b/artfynd/A 36424-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109573843</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135488702</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109573811</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,6 +1138,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134984551</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109573850</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135381716</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1453,6 +1488,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135381794</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1568,6 +1608,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135381962</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1683,6 +1728,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135368736</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1798,6 +1848,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135531138</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1909,6 +1964,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135381412</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2016,6 +2076,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135489134</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2128,6 +2193,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135485432</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2240,6 +2310,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484109</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2347,6 +2422,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135486564</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2454,6 +2534,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134894134</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2574,6 +2659,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134984523</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2681,8 +2771,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484279</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 36424-2025 artfynd.xlsx
+++ b/artfynd/A 36424-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,7 +790,7 @@
         <v>135488702</v>
       </c>
       <c r="B3" t="n">
-        <v>96783</v>
+        <v>96827</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>134984551</v>
       </c>
       <c r="B5" t="n">
-        <v>96423</v>
+        <v>96467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>135381716</v>
       </c>
       <c r="B7" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135381794</v>
       </c>
       <c r="B8" t="n">
-        <v>58563</v>
+        <v>58568</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135381962</v>
       </c>
       <c r="B9" t="n">
-        <v>58563</v>
+        <v>58568</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>135368736</v>
       </c>
       <c r="B10" t="n">
-        <v>58260</v>
+        <v>58265</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>135531138</v>
       </c>
       <c r="B11" t="n">
-        <v>58260</v>
+        <v>58265</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>135381412</v>
       </c>
       <c r="B12" t="n">
-        <v>58134</v>
+        <v>58139</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>135489134</v>
       </c>
       <c r="B13" t="n">
-        <v>30293</v>
+        <v>30296</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>135485432</v>
       </c>
       <c r="B14" t="n">
-        <v>56539</v>
+        <v>56544</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>135484109</v>
       </c>
       <c r="B15" t="n">
-        <v>56706</v>
+        <v>56711</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>135486564</v>
       </c>
       <c r="B16" t="n">
-        <v>56706</v>
+        <v>56711</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2430,27 +2430,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134894134</v>
+        <v>135636494</v>
       </c>
       <c r="B17" t="n">
-        <v>98060</v>
+        <v>106949</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220785</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2461,17 +2461,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grinsvalls gamla tomt, Grinsvalls gamla tomt, Boh</t>
+          <t>Fröjdens, Fröjdens, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>321780</v>
+        <v>321649</v>
       </c>
       <c r="R17" t="n">
-        <v>6421911</v>
+        <v>6421869</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2495,22 +2495,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2525,24 +2525,24 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134894134</t>
+          <t>https://artportalen.se/Sighting/135636494</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134984523</v>
+        <v>134894134</v>
       </c>
       <c r="B18" t="n">
         <v>98060</v>
@@ -2570,32 +2570,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rätsvik, Boh</t>
+          <t>Grinsvalls gamla tomt, Grinsvalls gamla tomt, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>321789</v>
+        <v>321780</v>
       </c>
       <c r="R18" t="n">
-        <v>6421986</v>
+        <v>6421911</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2624,7 +2612,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2634,7 +2622,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2643,34 +2631,33 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134984523</t>
+          <t>https://artportalen.se/Sighting/134894134</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135484279</v>
+        <v>134984523</v>
       </c>
       <c r="B19" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,20 +2682,32 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fröjdens, Fröjdens, Boh</t>
+          <t>Rätsvik, Boh</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>321819</v>
+        <v>321789</v>
       </c>
       <c r="R19" t="n">
-        <v>6421968</v>
+        <v>6421986</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2732,22 +2731,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2756,22 +2755,135 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134984523</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135484279</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98104</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fröjdens, Fröjdens, Boh</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>321819</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6421968</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135484279</t>
         </is>
@@ -2797,6 +2909,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36424-2025 artfynd.xlsx
+++ b/artfynd/A 36424-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135488702</v>
       </c>
       <c r="B3" t="n">
-        <v>96827</v>
+        <v>96854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>134984551</v>
       </c>
       <c r="B5" t="n">
-        <v>96467</v>
+        <v>96494</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>135636494</v>
       </c>
       <c r="B17" t="n">
-        <v>106949</v>
+        <v>106976</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>134984523</v>
       </c>
       <c r="B19" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>135484279</v>
       </c>
       <c r="B20" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 36424-2025 artfynd.xlsx
+++ b/artfynd/A 36424-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109573811</v>
+        <v>135488702</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
+        <v>96859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,38 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Olseröd, Kungälvs kommun, Boh</t>
+          <t>Rätsvik, Rätsvik, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>321766</v>
+        <v>321409</v>
       </c>
       <c r="R3" t="n">
-        <v>6421953</v>
+        <v>6421493</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,22 +852,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera kuddar varav största 30x20cm</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,34 +881,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ville Henrik-Klemens</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ville Henrik-Klemens</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109573811</t>
+          <t>https://artportalen.se/Sighting/135488702</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134984551</v>
+        <v>109573811</v>
       </c>
       <c r="B4" t="n">
-        <v>96494</v>
+        <v>96348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,32 +932,24 @@
           <t>(Hedw.) Warnst.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rätsvik, Boh</t>
+          <t>Olseröd, Kungälvs kommun, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>321761</v>
+        <v>321766</v>
       </c>
       <c r="R4" t="n">
-        <v>6422058</v>
+        <v>6421953</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +973,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -991,12 +983,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,27 +1004,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Ville Henrik-Klemens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Ville Henrik-Klemens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134984551</t>
+          <t>https://artportalen.se/Sighting/109573811</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109573850</v>
+        <v>134984551</v>
       </c>
       <c r="B5" t="n">
-        <v>57950</v>
+        <v>96494</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,45 +1032,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Olseröd, Boh</t>
+          <t>Rätsvik, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>321647</v>
+        <v>321761</v>
       </c>
       <c r="R5" t="n">
-        <v>6421751</v>
+        <v>6422058</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,47 +1098,58 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ville Henrik-Klemens</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ville Henrik-Klemens</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109573850</t>
+          <t>https://artportalen.se/Sighting/134984551</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134894134</v>
+        <v>109573850</v>
       </c>
       <c r="B6" t="n">
-        <v>98060</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,37 +1157,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grinsvalls gamla tomt, Grinsvalls gamla tomt, Boh</t>
+          <t>Olseröd, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>321780</v>
+        <v>321647</v>
       </c>
       <c r="R6" t="n">
-        <v>6421911</v>
+        <v>6421751</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1204,29 +1219,19 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:32</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:32</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1234,27 +1239,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Ville Henrik-Klemens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Ville Henrik-Klemens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134894134</t>
+          <t>https://artportalen.se/Sighting/109573850</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134984523</v>
+        <v>135381716</v>
       </c>
       <c r="B7" t="n">
-        <v>98131</v>
+        <v>57977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,35 +1267,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1298,13 +1299,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>321789</v>
+        <v>321805</v>
       </c>
       <c r="R7" t="n">
-        <v>6421986</v>
+        <v>6421950</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,22 +1329,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,7 +1353,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1370,7 +1370,1522 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135381716</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135381794</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58568</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102987</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sädesärla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Motacilla alba</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rätsvik, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>321814</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6421975</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135381794</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135381962</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58568</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102987</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sädesärla</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Motacilla alba</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rätsvik, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>321827</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6421967</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135381962</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135368736</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58265</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rätsvik, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>321766</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6421912</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135368736</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135531138</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58265</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rätsvik, Boh</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>321805</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6421950</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135531138</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135381412</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58139</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rätsvik, Boh</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>321701</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6421894</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135381412</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135489134</v>
+      </c>
+      <c r="B13" t="n">
+        <v>30296</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>200985</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blanksvart trämyra</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lasius fuliginosus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Latreille, 1798)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rätsvik, Rätsvik, Boh</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>321409</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6421493</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135489134</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135485432</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56544</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fröjdens, Fröjdens, Boh</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>321811</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6421891</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135485432</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135484109</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56711</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fröjdens, Fröjdens, Boh</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>321811</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6421891</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484109</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135486564</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56711</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Marielund, Boh</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>321632</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6421605</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135486564</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135636494</v>
+      </c>
+      <c r="B17" t="n">
+        <v>106981</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fröjdens, Fröjdens, Boh</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>321649</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6421869</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135636494</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134894134</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Grinsvalls gamla tomt, Grinsvalls gamla tomt, Boh</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>321780</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6421911</v>
+      </c>
+      <c r="S18" t="n">
+        <v>7</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134894134</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134984523</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98131</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Rätsvik, Boh</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>321789</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6421986</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134984523</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135484279</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98136</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fröjdens, Fröjdens, Boh</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>321819</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6421968</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484279</t>
         </is>
       </c>
     </row>
@@ -1382,6 +2897,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36424-2025 artfynd.xlsx
+++ b/artfynd/A 36424-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135488702</v>
       </c>
       <c r="B3" t="n">
-        <v>96859</v>
+        <v>96861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>135636494</v>
       </c>
       <c r="B17" t="n">
-        <v>106981</v>
+        <v>106983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>135484279</v>
       </c>
       <c r="B20" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 36424-2025 artfynd.xlsx
+++ b/artfynd/A 36424-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135488702</v>
       </c>
       <c r="B3" t="n">
-        <v>96861</v>
+        <v>96878</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>135531138</v>
       </c>
       <c r="B11" t="n">
-        <v>58265</v>
+        <v>58267</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>135489134</v>
       </c>
       <c r="B13" t="n">
-        <v>30296</v>
+        <v>30298</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>135485432</v>
       </c>
       <c r="B14" t="n">
-        <v>56544</v>
+        <v>56546</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>135484109</v>
       </c>
       <c r="B15" t="n">
-        <v>56711</v>
+        <v>56713</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>135486564</v>
       </c>
       <c r="B16" t="n">
-        <v>56711</v>
+        <v>56713</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>135636494</v>
       </c>
       <c r="B17" t="n">
-        <v>106983</v>
+        <v>107003</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>135484279</v>
       </c>
       <c r="B20" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 36424-2025 artfynd.xlsx
+++ b/artfynd/A 36424-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135488702</v>
       </c>
       <c r="B3" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>135636494</v>
       </c>
       <c r="B17" t="n">
-        <v>107003</v>
+        <v>107005</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>135484279</v>
       </c>
       <c r="B20" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 36424-2025 artfynd.xlsx
+++ b/artfynd/A 36424-2025 artfynd.xlsx
@@ -2433,7 +2433,7 @@
         <v>135636494</v>
       </c>
       <c r="B17" t="n">
-        <v>107005</v>
+        <v>107006</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 36424-2025 artfynd.xlsx
+++ b/artfynd/A 36424-2025 artfynd.xlsx
@@ -2433,7 +2433,7 @@
         <v>135636494</v>
       </c>
       <c r="B17" t="n">
-        <v>107006</v>
+        <v>107007</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 36424-2025 artfynd.xlsx
+++ b/artfynd/A 36424-2025 artfynd.xlsx
@@ -2433,7 +2433,7 @@
         <v>135636494</v>
       </c>
       <c r="B17" t="n">
-        <v>107007</v>
+        <v>107013</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
